--- a/data/trans_dic/P24D-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 29,14</t>
+          <t>19,86; 29,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,49; 54,89</t>
+          <t>41,84; 54,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,2; 51,02</t>
+          <t>37,08; 50,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 41,8</t>
+          <t>25,86; 41,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 24,5</t>
+          <t>13,13; 24,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 67,41</t>
+          <t>51,78; 67,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,61; 47,89</t>
+          <t>32,49; 47,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,02; 45,01</t>
+          <t>29,23; 44,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 26,22</t>
+          <t>19,0; 26,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,51; 57,29</t>
+          <t>47,96; 57,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,99; 47,92</t>
+          <t>37,79; 47,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,4; 40,81</t>
+          <t>29,16; 40,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 35,87</t>
+          <t>27,05; 36,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,1; 54,57</t>
+          <t>44,04; 54,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,35; 53,2</t>
+          <t>41,94; 53,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,26; 42,69</t>
+          <t>26,25; 41,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 49,58</t>
+          <t>36,04; 49,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,43; 57,29</t>
+          <t>45,68; 57,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,14; 59,28</t>
+          <t>47,06; 59,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 50,96</t>
+          <t>37,53; 50,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,37; 39,07</t>
+          <t>30,89; 38,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,0; 53,89</t>
+          <t>46,65; 54,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,63; 54,48</t>
+          <t>45,72; 54,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,35; 43,47</t>
+          <t>32,44; 44,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,69; 44,26</t>
+          <t>30,8; 43,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,25; 53,46</t>
+          <t>40,88; 53,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,54; 41,89</t>
+          <t>30,49; 41,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 43,34</t>
+          <t>27,54; 43,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,34; 46,47</t>
+          <t>32,07; 46,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,83; 58,3</t>
+          <t>43,68; 57,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 39,33</t>
+          <t>26,36; 38,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,52; 48,49</t>
+          <t>33,49; 48,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,95; 43,85</t>
+          <t>33,16; 42,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,25; 53,64</t>
+          <t>44,24; 53,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,36; 38,95</t>
+          <t>30,19; 38,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,41; 43,58</t>
+          <t>32,5; 44,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,42; 34,01</t>
+          <t>25,74; 34,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 46,42</t>
+          <t>35,61; 45,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,15; 49,42</t>
+          <t>37,97; 49,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,95; 45,76</t>
+          <t>32,77; 46,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 41,61</t>
+          <t>29,9; 41,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 52,34</t>
+          <t>41,1; 53,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,71; 55,85</t>
+          <t>42,66; 55,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,04; 55,88</t>
+          <t>42,86; 55,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,79; 36,05</t>
+          <t>29,05; 36,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,71; 47,85</t>
+          <t>39,29; 47,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,49; 50,51</t>
+          <t>41,87; 50,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,73; 48,18</t>
+          <t>39,29; 48,53</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,83; 32,93</t>
+          <t>28,05; 33,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,71; 49,11</t>
+          <t>43,54; 49,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,76; 45,48</t>
+          <t>40,02; 45,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,66; 39,42</t>
+          <t>31,84; 39,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,9; 38,21</t>
+          <t>31,47; 37,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,22; 54,72</t>
+          <t>47,87; 54,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,95; 47,67</t>
+          <t>41,21; 47,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,4; 47,24</t>
+          <t>40,08; 47,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,06; 34,34</t>
+          <t>30,02; 33,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,96; 50,42</t>
+          <t>46,33; 50,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,38; 45,8</t>
+          <t>41,37; 45,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,3; 41,83</t>
+          <t>36,2; 41,63</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63548; 92455</t>
+          <t>63020; 92832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114538; 147972</t>
+          <t>112783; 148145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95711; 127827</t>
+          <t>92902; 126619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47074; 74402</t>
+          <t>46040; 73791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19583; 38221</t>
+          <t>20481; 38453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83489; 109103</t>
+          <t>83795; 108744</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54914; 80651</t>
+          <t>54720; 79536</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36784; 55146</t>
+          <t>35818; 54398</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88900; 124094</t>
+          <t>89905; 126297</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204988; 247178</t>
+          <t>206919; 247797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159151; 200756</t>
+          <t>158338; 199032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88349; 122641</t>
+          <t>87628; 121786</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>108487; 145391</t>
+          <t>109643; 148084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>178835; 221300</t>
+          <t>178596; 220663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141790; 178115</t>
+          <t>140410; 178431</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62282; 101253</t>
+          <t>62256; 98985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80602; 111578</t>
+          <t>81096; 110806</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>131901; 166352</t>
+          <t>132635; 167754</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127705; 160616</t>
+          <t>127498; 161630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66802; 91319</t>
+          <t>67241; 91096</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>197733; 246297</t>
+          <t>194703; 245438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>320099; 375006</t>
+          <t>324602; 377457</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276394; 330019</t>
+          <t>276904; 329047</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>134693; 180974</t>
+          <t>135078; 184002</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77952; 112420</t>
+          <t>78228; 110100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128908; 167044</t>
+          <t>127752; 166656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94357; 129430</t>
+          <t>94229; 129754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54826; 84147</t>
+          <t>53468; 84311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54683; 78572</t>
+          <t>54220; 79016</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100206; 133280</t>
+          <t>99861; 131584</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60693; 88591</t>
+          <t>59388; 87533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53015; 74473</t>
+          <t>51443; 74550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>143635; 185520</t>
+          <t>140270; 181030</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>239429; 290261</t>
+          <t>239388; 288625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162179; 208091</t>
+          <t>161321; 205608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>112698; 151548</t>
+          <t>113006; 154393</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102788; 137508</t>
+          <t>104069; 139003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>132328; 169143</t>
+          <t>129724; 167103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104685; 139272</t>
+          <t>106993; 140243</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69481; 99529</t>
+          <t>71283; 100516</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92690; 126666</t>
+          <t>91028; 125621</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114846; 150947</t>
+          <t>118526; 153227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109923; 143740</t>
+          <t>109788; 142748</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82257; 106798</t>
+          <t>81911; 106006</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>204044; 255500</t>
+          <t>205896; 255135</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>259207; 312353</t>
+          <t>256440; 306825</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223696; 272346</t>
+          <t>225737; 271711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>158262; 196879</t>
+          <t>160532; 198289</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>384310; 454734</t>
+          <t>387290; 456308</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>590891; 663949</t>
+          <t>588595; 664147</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>467578; 534850</t>
+          <t>470680; 539975</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261761; 325962</t>
+          <t>263266; 325930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>272592; 326520</t>
+          <t>268931; 323551</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>467390; 530327</t>
+          <t>463910; 527689</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>377594; 439527</t>
+          <t>379914; 442177</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>261133; 305334</t>
+          <t>259098; 304949</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>671967; 767700</t>
+          <t>671062; 759321</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1066822; 1170387</t>
+          <t>1075336; 1178002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>868127; 960933</t>
+          <t>868049; 964351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>534770; 616261</t>
+          <t>533230; 613310</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P24D-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 29,26</t>
+          <t>19,88; 30,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,84; 54,95</t>
+          <t>41,88; 53,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,08; 50,54</t>
+          <t>38,18; 50,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,86; 41,45</t>
+          <t>26,69; 41,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 24,65</t>
+          <t>12,61; 25,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,78; 67,19</t>
+          <t>51,31; 68,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,49; 47,23</t>
+          <t>32,43; 47,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,23; 44,4</t>
+          <t>29,89; 44,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,0; 26,69</t>
+          <t>18,75; 26,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,96; 57,44</t>
+          <t>47,21; 57,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,79; 47,51</t>
+          <t>38,29; 47,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 40,52</t>
+          <t>29,71; 40,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 36,54</t>
+          <t>26,88; 36,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,04; 54,42</t>
+          <t>43,7; 54,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,94; 53,3</t>
+          <t>42,13; 53,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 41,74</t>
+          <t>25,86; 39,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,04; 49,24</t>
+          <t>35,36; 48,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,68; 57,78</t>
+          <t>45,33; 57,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,06; 59,66</t>
+          <t>46,77; 59,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,53; 50,84</t>
+          <t>37,47; 51,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 38,94</t>
+          <t>31,62; 39,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 54,24</t>
+          <t>46,34; 54,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,72; 54,32</t>
+          <t>46,02; 54,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,44; 44,2</t>
+          <t>31,41; 41,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 43,35</t>
+          <t>31,12; 44,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,88; 53,33</t>
+          <t>41,36; 53,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,49; 41,99</t>
+          <t>30,55; 41,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,54; 43,43</t>
+          <t>31,07; 47,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,07; 46,74</t>
+          <t>32,19; 47,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,68; 57,56</t>
+          <t>43,57; 57,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,36; 38,86</t>
+          <t>25,93; 38,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,49; 48,54</t>
+          <t>34,8; 49,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,16; 42,79</t>
+          <t>33,41; 42,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,24; 53,34</t>
+          <t>44,15; 53,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 38,48</t>
+          <t>30,39; 38,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,5; 44,4</t>
+          <t>35,48; 46,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 34,38</t>
+          <t>25,43; 34,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,61; 45,86</t>
+          <t>35,71; 45,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,97; 49,77</t>
+          <t>37,81; 49,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,77; 46,22</t>
+          <t>32,87; 46,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 41,27</t>
+          <t>30,09; 41,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,1; 53,13</t>
+          <t>40,13; 52,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,66; 55,46</t>
+          <t>42,82; 54,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,86; 55,47</t>
+          <t>43,68; 56,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 36,0</t>
+          <t>28,95; 35,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,29; 47,01</t>
+          <t>39,31; 47,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,87; 50,39</t>
+          <t>42,06; 50,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,29; 48,53</t>
+          <t>39,67; 48,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 33,05</t>
+          <t>28,03; 33,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,54; 49,13</t>
+          <t>43,47; 49,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,02; 45,91</t>
+          <t>40,02; 45,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,84; 39,42</t>
+          <t>31,92; 39,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,47; 37,87</t>
+          <t>31,4; 37,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,87; 54,45</t>
+          <t>47,64; 54,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,21; 47,96</t>
+          <t>41,41; 47,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,08; 47,18</t>
+          <t>40,3; 46,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,02; 33,97</t>
+          <t>30,15; 34,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,33; 50,75</t>
+          <t>45,98; 50,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,37; 45,96</t>
+          <t>41,47; 45,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,2; 41,63</t>
+          <t>36,86; 41,98</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104239</t>
+          <t>111932</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63020; 92832</t>
+          <t>63074; 95254</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112783; 148145</t>
+          <t>112895; 145527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92902; 126619</t>
+          <t>95664; 127515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46040; 73791</t>
+          <t>51479; 80502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20481; 38453</t>
+          <t>19671; 39453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83795; 108744</t>
+          <t>83047; 110961</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54720; 79536</t>
+          <t>54607; 79298</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35818; 54398</t>
+          <t>38822; 57577</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89905; 126297</t>
+          <t>88721; 125834</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206919; 247797</t>
+          <t>203671; 248643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158338; 199032</t>
+          <t>160438; 198709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87628; 121786</t>
+          <t>95908; 131604</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78837</t>
+          <t>81336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78976</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>157813</t>
+          <t>166301</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>109643; 148084</t>
+          <t>108936; 147157</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>178596; 220663</t>
+          <t>177220; 220266</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140410; 178431</t>
+          <t>141062; 178877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62256; 98985</t>
+          <t>65694; 100062</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81096; 110806</t>
+          <t>79564; 108945</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132635; 167754</t>
+          <t>131611; 167169</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127498; 161630</t>
+          <t>126708; 160751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67241; 91096</t>
+          <t>72988; 99333</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194703; 245438</t>
+          <t>199331; 247372</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>324602; 377457</t>
+          <t>322457; 376529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276904; 329047</t>
+          <t>278775; 328271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135078; 184002</t>
+          <t>140961; 187160</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>80128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63180</t>
+          <t>72358</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>132056</t>
+          <t>152486</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78228; 110100</t>
+          <t>79040; 111919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127752; 166656</t>
+          <t>129232; 165930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94229; 129754</t>
+          <t>94407; 128466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53468; 84311</t>
+          <t>64575; 98443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54220; 79016</t>
+          <t>54420; 79482</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>99861; 131584</t>
+          <t>99604; 131898</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59388; 87533</t>
+          <t>58401; 87563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51443; 74550</t>
+          <t>59648; 84251</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>140270; 181030</t>
+          <t>141354; 181599</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>239388; 288625</t>
+          <t>238878; 287567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161321; 205608</t>
+          <t>162366; 208015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>113006; 154393</t>
+          <t>134550; 176387</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84323</t>
+          <t>94160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>101984</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>178895</t>
+          <t>196144</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>104069; 139003</t>
+          <t>102812; 139823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129724; 167103</t>
+          <t>130090; 166918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106993; 140243</t>
+          <t>106534; 139403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71283; 100516</t>
+          <t>78731; 112063</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91028; 125621</t>
+          <t>91607; 126092</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118526; 153227</t>
+          <t>115720; 150566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109788; 142748</t>
+          <t>110220; 141297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81911; 106006</t>
+          <t>89488; 115274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>205896; 255135</t>
+          <t>205149; 252327</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>256440; 306825</t>
+          <t>256609; 309564</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>225737; 271711</t>
+          <t>226775; 271477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>160532; 198289</t>
+          <t>176315; 216227</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>387290; 456308</t>
+          <t>387022; 457836</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>588595; 664147</t>
+          <t>587726; 662984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>470680; 539975</t>
+          <t>470649; 540294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263266; 325930</t>
+          <t>285482; 353950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>268931; 323551</t>
+          <t>268296; 324646</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>463910; 527689</t>
+          <t>461690; 528034</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379914; 442177</t>
+          <t>381797; 441009</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>259098; 304949</t>
+          <t>282477; 329045</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>671062; 759321</t>
+          <t>673899; 762196</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1075336; 1178002</t>
+          <t>1067264; 1169235</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>868049; 964351</t>
+          <t>870043; 961813</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>533230; 613310</t>
+          <t>588102; 669762</t>
         </is>
       </c>
     </row>
